--- a/InputData/elec/MCF/Maximum Capacity Factor.xlsx
+++ b/InputData/elec/MCF/Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\MCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F8901C8-0A08-45FE-BA2D-BF915959C34A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4EA080-2835-46E2-ACAA-C8B525FFB4D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -1850,12 +1850,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" customWidth="1"/>
-    <col min="2" max="2" width="50.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="49.54296875" customWidth="1"/>
-    <col min="8" max="8" width="53.7265625" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="49.5703125" customWidth="1"/>
+    <col min="8" max="8" width="53.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -2014,11 +2014,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0150863A-DAB8-46CE-A81F-C1B3C520912B}">
   <dimension ref="A1:N158"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="65.26953125" style="58" customWidth="1"/>
+    <col min="1" max="1" width="65.28515625" style="58" customWidth="1"/>
     <col min="2" max="2" width="2" style="58" customWidth="1"/>
-    <col min="3" max="8" width="8.453125" style="9" customWidth="1"/>
+    <col min="3" max="8" width="8.42578125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
@@ -2030,7 +2030,7 @@
       <c r="F1" s="8"/>
       <c r="G1"/>
     </row>
-    <row r="2" spans="1:14" ht="25">
+    <row r="2" spans="1:14" ht="26.25">
       <c r="A2" s="102" t="s">
         <v>35</v>
       </c>
@@ -2074,7 +2074,7 @@
       <c r="F5" s="8"/>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:14" ht="15.5">
+    <row r="6" spans="1:14" ht="15.75">
       <c r="A6" s="10"/>
       <c r="B6" s="10"/>
       <c r="C6" s="10" t="s">
@@ -2103,7 +2103,7 @@
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
     </row>
-    <row r="9" spans="1:14" ht="15" thickBot="1">
+    <row r="9" spans="1:14" ht="15.75" thickBot="1">
       <c r="A9" s="13" t="s">
         <v>38</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="18.5" thickBot="1">
+    <row r="10" spans="1:14" ht="18.75" thickBot="1">
       <c r="A10" s="15" t="s">
         <v>40</v>
       </c>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="J14" s="37"/>
     </row>
-    <row r="15" spans="1:14" ht="15" thickBot="1">
+    <row r="15" spans="1:14" ht="15.75" thickBot="1">
       <c r="A15" s="38" t="s">
         <v>45</v>
       </c>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J15" s="37"/>
     </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1">
       <c r="A16" s="21"/>
       <c r="B16" s="21"/>
       <c r="C16" s="43"/>
@@ -2290,7 +2290,7 @@
       <c r="G16" s="43"/>
       <c r="H16" s="44"/>
     </row>
-    <row r="17" spans="1:10" ht="18.5" thickBot="1">
+    <row r="17" spans="1:10" ht="18.75" thickBot="1">
       <c r="A17" s="15" t="s">
         <v>46</v>
       </c>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="J17" s="19"/>
     </row>
-    <row r="18" spans="1:10" ht="15" thickBot="1">
+    <row r="18" spans="1:10" ht="15.75" thickBot="1">
       <c r="A18" s="45" t="s">
         <v>47</v>
       </c>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="J18" s="49"/>
     </row>
-    <row r="19" spans="1:10" ht="15" thickBot="1">
+    <row r="19" spans="1:10" ht="15.75" thickBot="1">
       <c r="A19" s="21"/>
       <c r="B19" s="21"/>
       <c r="C19" s="50"/>
@@ -2356,7 +2356,7 @@
       <c r="G19" s="50"/>
       <c r="H19" s="51"/>
     </row>
-    <row r="20" spans="1:10" ht="18.5" thickBot="1">
+    <row r="20" spans="1:10" ht="18.75" thickBot="1">
       <c r="A20" s="15" t="s">
         <v>48</v>
       </c>
@@ -2619,7 +2619,7 @@
       </c>
       <c r="J30" s="54"/>
     </row>
-    <row r="31" spans="1:10" ht="15" thickBot="1">
+    <row r="31" spans="1:10" ht="15.75" thickBot="1">
       <c r="A31" s="61" t="s">
         <v>59</v>
       </c>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="J31" s="54"/>
     </row>
-    <row r="32" spans="1:10" ht="15" thickBot="1">
+    <row r="32" spans="1:10" ht="15.75" thickBot="1">
       <c r="A32" s="21"/>
       <c r="B32" s="21"/>
       <c r="C32" s="65"/>
@@ -2657,7 +2657,7 @@
       <c r="G32" s="65"/>
       <c r="H32" s="65"/>
     </row>
-    <row r="33" spans="1:10" ht="18.5" thickBot="1">
+    <row r="33" spans="1:10" ht="18.75" thickBot="1">
       <c r="A33" s="15" t="s">
         <v>60</v>
       </c>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="J37" s="68"/>
     </row>
-    <row r="38" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="38" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A38" s="57" t="s">
         <v>65</v>
       </c>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="J38" s="68"/>
     </row>
-    <row r="39" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="39" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A39" s="59" t="s">
         <v>66</v>
       </c>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="J39" s="68"/>
     </row>
-    <row r="40" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="40" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A40" s="57" t="s">
         <v>67</v>
       </c>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="J40" s="68"/>
     </row>
-    <row r="41" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="41" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A41" s="59" t="s">
         <v>68</v>
       </c>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="J42" s="68"/>
     </row>
-    <row r="43" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="43" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A43" s="59" t="s">
         <v>70</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="J43" s="68"/>
     </row>
-    <row r="44" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="44" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A44" s="57" t="s">
         <v>71</v>
       </c>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="J44" s="68"/>
     </row>
-    <row r="45" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="45" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A45" s="59" t="s">
         <v>72</v>
       </c>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="J48" s="68"/>
     </row>
-    <row r="49" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="49" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A49" s="59" t="s">
         <v>76</v>
       </c>
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J49" s="68"/>
     </row>
-    <row r="50" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="50" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A50" s="57" t="s">
         <v>77</v>
       </c>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="J53" s="68"/>
     </row>
-    <row r="54" spans="1:10" ht="15" thickBot="1">
+    <row r="54" spans="1:10" ht="15.75" thickBot="1">
       <c r="A54" s="76" t="s">
         <v>81</v>
       </c>
@@ -3269,7 +3269,7 @@
       </c>
       <c r="J54" s="68"/>
     </row>
-    <row r="55" spans="1:10" ht="15.5" thickTop="1" thickBot="1">
+    <row r="55" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="A55" s="21"/>
       <c r="B55" s="21"/>
       <c r="C55" s="66"/>
@@ -3279,7 +3279,7 @@
       <c r="G55" s="66"/>
       <c r="H55" s="66"/>
     </row>
-    <row r="56" spans="1:10" ht="18.5" thickBot="1">
+    <row r="56" spans="1:10" ht="18.75" thickBot="1">
       <c r="A56" s="15" t="s">
         <v>82</v>
       </c>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="J60" s="81"/>
     </row>
-    <row r="61" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="61" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A61" s="57" t="s">
         <v>65</v>
       </c>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="J61" s="81"/>
     </row>
-    <row r="62" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="62" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A62" s="59" t="s">
         <v>66</v>
       </c>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="J62" s="81"/>
     </row>
-    <row r="63" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="63" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A63" s="57" t="s">
         <v>67</v>
       </c>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="J64" s="81"/>
     </row>
-    <row r="65" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="65" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A65" s="57" t="s">
         <v>70</v>
       </c>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="J65" s="81"/>
     </row>
-    <row r="66" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="66" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A66" s="82" t="s">
         <v>71</v>
       </c>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="J66" s="81"/>
     </row>
-    <row r="67" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="67" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A67" s="57" t="s">
         <v>72</v>
       </c>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="J70" s="81"/>
     </row>
-    <row r="71" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="71" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A71" s="57" t="s">
         <v>76</v>
       </c>
@@ -3727,7 +3727,7 @@
       </c>
       <c r="J71" s="81"/>
     </row>
-    <row r="72" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="72" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A72" s="83" t="s">
         <v>77</v>
       </c>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="J74" s="81"/>
     </row>
-    <row r="75" spans="1:10" ht="15" thickBot="1">
+    <row r="75" spans="1:10" ht="15.75" thickBot="1">
       <c r="A75" s="84" t="s">
         <v>81</v>
       </c>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="J75" s="81"/>
     </row>
-    <row r="76" spans="1:10" ht="15" thickBot="1">
+    <row r="76" spans="1:10" ht="15.75" thickBot="1">
       <c r="A76" s="38"/>
       <c r="B76" s="39"/>
       <c r="C76" s="88"/>
@@ -3851,7 +3851,7 @@
       <c r="I76" s="88"/>
       <c r="J76" s="81"/>
     </row>
-    <row r="77" spans="1:10" ht="18.5" thickBot="1">
+    <row r="77" spans="1:10" ht="18.75" thickBot="1">
       <c r="A77" s="15" t="s">
         <v>83</v>
       </c>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="J81" s="81"/>
     </row>
-    <row r="82" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="82" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A82" s="57" t="s">
         <v>65</v>
       </c>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="J82" s="81"/>
     </row>
-    <row r="83" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="83" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A83" s="59" t="s">
         <v>66</v>
       </c>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="J83" s="81"/>
     </row>
-    <row r="84" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="84" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A84" s="57" t="s">
         <v>67</v>
       </c>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="J85" s="81"/>
     </row>
-    <row r="86" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="86" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A86" s="57" t="s">
         <v>70</v>
       </c>
@@ -4131,7 +4131,7 @@
       </c>
       <c r="J86" s="81"/>
     </row>
-    <row r="87" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="87" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A87" s="82" t="s">
         <v>71</v>
       </c>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="J87" s="81"/>
     </row>
-    <row r="88" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="88" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A88" s="57" t="s">
         <v>72</v>
       </c>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="J91" s="81"/>
     </row>
-    <row r="92" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="92" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A92" s="57" t="s">
         <v>76</v>
       </c>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="J92" s="81"/>
     </row>
-    <row r="93" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="93" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A93" s="83" t="s">
         <v>77</v>
       </c>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="J95" s="81"/>
     </row>
-    <row r="96" spans="1:10" ht="15" thickBot="1">
+    <row r="96" spans="1:10" ht="15.75" thickBot="1">
       <c r="A96" s="84" t="s">
         <v>81</v>
       </c>
@@ -4411,7 +4411,7 @@
       </c>
       <c r="J96" s="81"/>
     </row>
-    <row r="97" spans="1:10" ht="15" thickBot="1">
+    <row r="97" spans="1:10" ht="15.75" thickBot="1">
       <c r="A97" s="21"/>
       <c r="B97" s="21"/>
       <c r="C97" s="66"/>
@@ -4421,7 +4421,7 @@
       <c r="G97" s="66"/>
       <c r="H97" s="66"/>
     </row>
-    <row r="98" spans="1:10" ht="18.5" thickBot="1">
+    <row r="98" spans="1:10" ht="18.75" thickBot="1">
       <c r="A98" s="15" t="s">
         <v>84</v>
       </c>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="J110" s="68"/>
     </row>
-    <row r="111" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="111" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A111" s="58" t="s">
         <v>97</v>
       </c>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="J111" s="68"/>
     </row>
-    <row r="112" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="112" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A112" s="60" t="s">
         <v>98</v>
       </c>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="J112" s="68"/>
     </row>
-    <row r="113" spans="1:10" s="73" customFormat="1" thickBot="1">
+    <row r="113" spans="1:10" s="73" customFormat="1" ht="15.75" thickBot="1">
       <c r="A113" s="84" t="s">
         <v>81</v>
       </c>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="J113" s="68"/>
     </row>
-    <row r="114" spans="1:10" s="73" customFormat="1" ht="15" thickBot="1">
+    <row r="114" spans="1:10" s="73" customFormat="1" ht="15.75" thickBot="1">
       <c r="A114" s="58"/>
       <c r="B114" s="58"/>
       <c r="C114" s="66"/>
@@ -4874,7 +4874,7 @@
       <c r="I114"/>
       <c r="J114" s="68"/>
     </row>
-    <row r="115" spans="1:10" s="73" customFormat="1" ht="18.5" thickBot="1">
+    <row r="115" spans="1:10" s="73" customFormat="1" ht="18.75" thickBot="1">
       <c r="A115" s="15" t="s">
         <v>99</v>
       </c>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="J115" s="68"/>
     </row>
-    <row r="116" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="116" spans="1:10" s="73" customFormat="1">
       <c r="A116" s="20" t="s">
         <v>61</v>
       </c>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="J117" s="92"/>
     </row>
-    <row r="118" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="118" spans="1:10" s="73" customFormat="1">
       <c r="A118" s="57" t="s">
         <v>63</v>
       </c>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="J118" s="68"/>
     </row>
-    <row r="119" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="119" spans="1:10" s="73" customFormat="1">
       <c r="A119" s="59" t="s">
         <v>100</v>
       </c>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="J119" s="68"/>
     </row>
-    <row r="120" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="120" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A120" s="57" t="s">
         <v>64</v>
       </c>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="J124" s="68"/>
     </row>
-    <row r="125" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="125" spans="1:10" s="73" customFormat="1">
       <c r="A125" s="27" t="s">
         <v>69</v>
       </c>
@@ -5180,7 +5180,7 @@
       </c>
       <c r="J125" s="68"/>
     </row>
-    <row r="126" spans="1:10" s="73" customFormat="1" ht="14">
+    <row r="126" spans="1:10" s="73" customFormat="1" ht="14.25">
       <c r="A126" s="57" t="s">
         <v>101</v>
       </c>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="J136" s="68"/>
     </row>
-    <row r="137" spans="1:10" ht="15" thickBot="1">
+    <row r="137" spans="1:10" ht="15.75" thickBot="1">
       <c r="A137" s="93" t="s">
         <v>81</v>
       </c>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="J137" s="68"/>
     </row>
-    <row r="138" spans="1:10" ht="15.5" thickTop="1" thickBot="1">
+    <row r="138" spans="1:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="A138" s="21"/>
       <c r="B138" s="21"/>
       <c r="C138" s="66"/>
@@ -5521,7 +5521,7 @@
       <c r="H138" s="66"/>
       <c r="J138" s="68"/>
     </row>
-    <row r="139" spans="1:10" ht="18.5" thickBot="1">
+    <row r="139" spans="1:10" ht="18.75" thickBot="1">
       <c r="A139" s="15" t="s">
         <v>102</v>
       </c>
@@ -5928,7 +5928,7 @@
       <c r="H155" s="69"/>
       <c r="I155" s="70"/>
     </row>
-    <row r="156" spans="1:10" ht="15" thickBot="1">
+    <row r="156" spans="1:10" ht="15.75" thickBot="1">
       <c r="A156" s="38" t="s">
         <v>115</v>
       </c>
@@ -5987,12 +5987,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4E39369-50AE-4D5B-A91E-C3BF3A8489A4}">
   <dimension ref="A1:AE9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="18.5" thickBot="1">
+    <row r="1" spans="1:31" ht="18.75" thickBot="1">
       <c r="B1" s="17">
         <v>2028</v>
       </c>
@@ -6347,7 +6347,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0277EEC5-A757-48AB-8FE9-C61BFB5A988F}">
   <dimension ref="A1:AE27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:31">
       <c r="A1" t="s">
@@ -8740,13 +8740,13 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:AE25"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="26.453125" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="29">
+    <row r="1" spans="1:31" ht="30">
       <c r="A1" s="6" t="s">
         <v>16</v>
       </c>
@@ -8846,124 +8846,94 @@
         <v>10</v>
       </c>
       <c r="B2" s="3">
-        <f>'Coal Calculations'!B9</f>
         <v>0.85</v>
       </c>
       <c r="C2" s="3">
-        <f>'Coal Calculations'!C9</f>
         <v>0.85</v>
       </c>
       <c r="D2" s="3">
-        <f>'Coal Calculations'!D9</f>
         <v>0.85</v>
       </c>
       <c r="E2" s="3">
-        <f>'Coal Calculations'!E9</f>
         <v>0.85</v>
       </c>
       <c r="F2" s="3">
-        <f>'Coal Calculations'!F9</f>
         <v>0.85</v>
       </c>
       <c r="G2" s="3">
-        <f>'Coal Calculations'!G9</f>
         <v>0.85</v>
       </c>
       <c r="H2" s="3">
-        <f>'Coal Calculations'!H9</f>
         <v>0.85</v>
       </c>
       <c r="I2" s="3">
-        <f>'Coal Calculations'!I9</f>
         <v>0.85</v>
       </c>
       <c r="J2" s="3">
-        <f>'Coal Calculations'!J9</f>
         <v>0.85</v>
       </c>
       <c r="K2" s="3">
-        <f>'Coal Calculations'!K9</f>
         <v>0.85</v>
       </c>
       <c r="L2" s="3">
-        <f>'Coal Calculations'!L9</f>
         <v>0.85</v>
       </c>
       <c r="M2" s="3">
-        <f>'Coal Calculations'!M9</f>
         <v>0.85</v>
       </c>
       <c r="N2" s="3">
-        <f>'Coal Calculations'!N9</f>
         <v>0.85</v>
       </c>
       <c r="O2" s="3">
-        <f>'Coal Calculations'!O9</f>
         <v>0.85</v>
       </c>
       <c r="P2" s="3">
-        <f>'Coal Calculations'!P9</f>
         <v>0.85</v>
       </c>
       <c r="Q2" s="3">
-        <f>'Coal Calculations'!Q9</f>
-        <v>0.72031265723109072</v>
+        <v>0.85</v>
       </c>
       <c r="R2" s="3">
-        <f>'Coal Calculations'!R9</f>
-        <v>0.59062531446215871</v>
+        <v>0.85</v>
       </c>
       <c r="S2" s="3">
-        <f>'Coal Calculations'!S9</f>
-        <v>0.4609379716932267</v>
+        <v>0.85</v>
       </c>
       <c r="T2" s="3">
-        <f>'Coal Calculations'!T9</f>
-        <v>0.33125062892429469</v>
+        <v>0.85</v>
       </c>
       <c r="U2" s="3">
-        <f>'Coal Calculations'!U9</f>
-        <v>0.20156328615530583</v>
+        <v>0.85</v>
       </c>
       <c r="V2" s="3">
-        <f>'Coal Calculations'!V9</f>
-        <v>0.19321882697840209</v>
+        <v>0.85</v>
       </c>
       <c r="W2" s="3">
-        <f>'Coal Calculations'!W9</f>
-        <v>0.18487436780148059</v>
+        <v>0.85</v>
       </c>
       <c r="X2" s="3">
-        <f>'Coal Calculations'!X9</f>
-        <v>0.17652990862455908</v>
+        <v>0.85</v>
       </c>
       <c r="Y2" s="3">
-        <f>'Coal Calculations'!Y9</f>
-        <v>0.16818544944764113</v>
+        <v>0.85</v>
       </c>
       <c r="Z2" s="3">
-        <f>'Coal Calculations'!Z9</f>
-        <v>0.15984099027071963</v>
+        <v>0.85</v>
       </c>
       <c r="AA2" s="3">
-        <f>'Coal Calculations'!AA9</f>
-        <v>0.23406504492902513</v>
+        <v>0.85</v>
       </c>
       <c r="AB2" s="3">
-        <f>'Coal Calculations'!AB9</f>
-        <v>0.3082890995873413</v>
+        <v>0.85</v>
       </c>
       <c r="AC2" s="3">
-        <f>'Coal Calculations'!AC9</f>
-        <v>0.38251315424565746</v>
+        <v>0.85</v>
       </c>
       <c r="AD2" s="3">
-        <f>'Coal Calculations'!AD9</f>
-        <v>0.45673720890397362</v>
+        <v>0.85</v>
       </c>
       <c r="AE2" s="3">
-        <f>'Coal Calculations'!AE9</f>
-        <v>0.53096126356228979</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="3" spans="1:31">
@@ -10552,63 +10522,63 @@
       </c>
       <c r="Q19" s="3">
         <f t="shared" si="0"/>
-        <v>0.72031265723109072</v>
+        <v>0.85</v>
       </c>
       <c r="R19" s="3">
         <f t="shared" si="0"/>
-        <v>0.59062531446215871</v>
+        <v>0.85</v>
       </c>
       <c r="S19" s="3">
         <f t="shared" si="0"/>
-        <v>0.4609379716932267</v>
+        <v>0.85</v>
       </c>
       <c r="T19" s="3">
         <f t="shared" si="0"/>
-        <v>0.33125062892429469</v>
+        <v>0.85</v>
       </c>
       <c r="U19" s="3">
         <f t="shared" si="0"/>
-        <v>0.20156328615530583</v>
+        <v>0.85</v>
       </c>
       <c r="V19" s="3">
         <f t="shared" si="0"/>
-        <v>0.19321882697840209</v>
+        <v>0.85</v>
       </c>
       <c r="W19" s="3">
         <f t="shared" si="0"/>
-        <v>0.18487436780148059</v>
+        <v>0.85</v>
       </c>
       <c r="X19" s="3">
         <f t="shared" si="0"/>
-        <v>0.17652990862455908</v>
+        <v>0.85</v>
       </c>
       <c r="Y19" s="3">
         <f t="shared" si="0"/>
-        <v>0.16818544944764113</v>
+        <v>0.85</v>
       </c>
       <c r="Z19" s="3">
         <f t="shared" si="0"/>
-        <v>0.15984099027071963</v>
+        <v>0.85</v>
       </c>
       <c r="AA19" s="3">
         <f t="shared" si="0"/>
-        <v>0.23406504492902513</v>
+        <v>0.85</v>
       </c>
       <c r="AB19" s="3">
         <f t="shared" si="0"/>
-        <v>0.3082890995873413</v>
+        <v>0.85</v>
       </c>
       <c r="AC19" s="3">
         <f t="shared" si="0"/>
-        <v>0.38251315424565746</v>
+        <v>0.85</v>
       </c>
       <c r="AD19" s="3">
         <f t="shared" si="0"/>
-        <v>0.45673720890397362</v>
+        <v>0.85</v>
       </c>
       <c r="AE19" s="3">
         <f t="shared" si="0"/>
-        <v>0.53096126356228979</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="20" spans="1:31">
